--- a/data/processed/peer_groups.xlsx
+++ b/data/processed/peer_groups.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,7 +836,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>BAJAJAUTO</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -854,7 +854,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -872,7 +872,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -890,25 +890,25 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="D27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -917,16 +917,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -944,7 +944,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -962,25 +962,25 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="D31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -989,16 +989,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -1052,25 +1052,25 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="D36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1079,16 +1079,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="D37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -1106,7 +1106,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -1124,7 +1124,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -1178,25 +1178,25 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -1250,25 +1250,25 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1277,16 +1277,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -1304,7 +1304,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -1322,7 +1322,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -1340,7 +1340,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -1358,7 +1358,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -1376,25 +1376,25 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1403,28 +1403,46 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="D55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Consumer Finance</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Consumer Finance</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="D56" t="b">
+      <c r="D57" t="b">
         <v>0</v>
       </c>
     </row>
